--- a/healthcare_forms/034_influenza_vaccination_consent_form--healthcare_forms.xlsx
+++ b/healthcare_forms/034_influenza_vaccination_consent_form--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>allergic_to_shellfish</t>
+          <t>allergic_to_sulfites</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Allergic to shellfish</t>
+          <t>Allergic to sulfites</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>allergic_to_sulfites</t>
+          <t>allergic_to_strawberries</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Allergic to sulfites</t>
+          <t>Allergic to strawberries</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>allergic_to_strawberries</t>
+          <t>allergic_to_bananas</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Allergic to strawberries</t>
+          <t>Allergic to bananas</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>allergic_to_bananas</t>
+          <t>allergic_to_apples</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Allergic to bananas</t>
+          <t>Allergic to apples</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>allergic_to_apples</t>
+          <t>allergic_to_oranges</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Allergic to apples</t>
+          <t>Allergic to oranges</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>allergic_to_oranges</t>
+          <t>allergic_to_lemons</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Allergic to oranges</t>
+          <t>Allergic to lemons</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>allergic_to_lemons</t>
+          <t>allergic_to_limes</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Allergic to lemons</t>
+          <t>Allergic to limes</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>allergic_to_limes</t>
+          <t>allergic_to_avocados</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Allergic to limes</t>
+          <t>Allergic to avocados</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>allergic_to_avocados</t>
+          <t>allergic_to_pears</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Allergic to avocados</t>
+          <t>Allergic to pears</t>
         </is>
       </c>
     </row>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>allergic_to_pears</t>
+          <t>allergic_to_water</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Allergic to pears</t>
+          <t>Allergic to water</t>
         </is>
       </c>
     </row>
@@ -1475,29 +1475,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>allergic_to_water</t>
+          <t>allergic_to_wheat</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Allergic to water</t>
+          <t>Allergic to wheat</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>medical_condition_choices</t>
+          <t>flu_vaccination_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>allergic_to_wheat</t>
+          <t>flumist</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Allergic to wheat</t>
+          <t>FluMist</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1509,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>flumist</t>
+          <t>fluloose</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>FluMist</t>
+          <t>FluLoose</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>fluloose</t>
+          <t>flumist+fluloose</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>FluLoose</t>
+          <t>FluMist+FluLoose</t>
         </is>
       </c>
     </row>
@@ -1543,12 +1543,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>flumist+fluloose</t>
+          <t>flumist+flumist</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>FluMist+FluLoose</t>
+          <t>FluMist+FluMist</t>
         </is>
       </c>
     </row>
@@ -1560,12 +1560,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>flumist+flumist</t>
+          <t>fluloose+flumist</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FluMist+FluMist</t>
+          <t>FluLoose+FluMist</t>
         </is>
       </c>
     </row>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>fluloose+flumist</t>
+          <t>fluloose+fluloose</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FluLoose+FluMist</t>
+          <t>FluLoose+FluLoose</t>
         </is>
       </c>
     </row>
@@ -1594,12 +1594,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>fluloose+fluloose</t>
+          <t>fluloose+flumist+flumist</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FluLoose+FluLoose</t>
+          <t>FluLoose+FluMist+FluMist</t>
         </is>
       </c>
     </row>
@@ -1611,12 +1611,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>flumist+fluloose</t>
+          <t>flumist+fluloose+flumist</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FluMist+FluLoose</t>
+          <t>FluMist+FluLoose+FluMist</t>
         </is>
       </c>
     </row>
@@ -1628,12 +1628,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>fluloose+flumist+flumist</t>
+          <t>fluloose+fluloose+flumist</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>FluLoose+FluMist+FluMist</t>
+          <t>FluLoose+FluLoose+FluMist</t>
         </is>
       </c>
     </row>
@@ -1645,80 +1645,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>flumist</t>
+          <t>flumist+flumist+fluloose</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>FluMist</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>flu_vaccination_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>flumist+fluloose+flumist</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>FluMist+FluLoose+FluMist</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>flu_vaccination_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>fluloose+fluloose+flumist</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>FluLoose+FluLoose+FluMist</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>flu_vaccination_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>flumist+flumist+fluloose</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
           <t>FluMist+FluMist+FluLoose</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>flu_vaccination_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>fluloose</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>FluLoose</t>
         </is>
       </c>
     </row>
